--- a/tables_and_figures/table4_jaccard_average_questionnaires.xlsx
+++ b/tables_and_figures/table4_jaccard_average_questionnaires.xlsx
@@ -426,21 +426,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRAQ</t>
+          <t>SAQLI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5927621760955094</v>
+        <v>0.5764482431149097</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAQLI</t>
+          <t>OSAPOSI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5764482431149097</v>
+        <v>0.517667209333876</v>
       </c>
     </row>
     <row r="4">
@@ -456,31 +456,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAPOSI</t>
+          <t>MOSAS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.517667209333876</v>
+        <v>0.3852731375951191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STAMP</t>
+          <t>PRAQ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3119372505337417</v>
+        <v>0.5927621760955094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MOSAS</t>
+          <t>STAMP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3852731375951191</v>
+        <v>0.3119372505337418</v>
       </c>
     </row>
     <row r="8">
